--- a/reports/16_loyal_users_revenue_lmau.xlsx
+++ b/reports/16_loyal_users_revenue_lmau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DIMA\ОБУЧЕНИЕ\практика\project-planet-hunt-sql-analysis\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCFE848E-A6A1-4619-AE35-63C86A6A7C7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22C71A07-06E5-4BF8-81CC-7BDAA7D804D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{E1172667-8E28-451B-A28D-EB949B25813B}"/>
   </bookViews>
@@ -610,12 +610,7 @@
       <a:schemeClr val="tx1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
